--- a/data/trans_dic/P36$huevo-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P36$huevo-Provincia-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que desayuna, al menos, alimentos como huevos, queso, jamón</t>
+          <t>Población que desayuna, al menos, alimentos como huevos, queso, jamón (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,32 +678,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,47</t>
+          <t>0,35; 3,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,61; 3,85</t>
+          <t>0,65; 3,9</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,77; 6,49</t>
+          <t>1,74; 6,11</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,9</t>
+          <t>0,0; 1,92</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,39; 3,6</t>
+          <t>0,4; 3,83</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,61; 3,68</t>
+          <t>0,63; 3,82</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,76; 3,18</t>
+          <t>0,73; 3,1</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,54; 4,12</t>
+          <t>1,6; 4,24</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,64; 3,68</t>
+          <t>0,76; 3,66</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,66; 4,64</t>
+          <t>1,74; 4,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,01</t>
+          <t>0,0; 1,02</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,71</t>
+          <t>0,18; 1,76</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,93; 4,08</t>
+          <t>0,93; 4,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,4</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,6; 2,3</t>
+          <t>0,58; 2,18</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,62; 3,77</t>
+          <t>1,66; 3,65</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,46</t>
+          <t>0,0; 0,54</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,26; 4,76</t>
+          <t>1,26; 5,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,25; 12,32</t>
+          <t>6,21; 12,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,75; 7,51</t>
+          <t>2,92; 7,53</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,88; 4,03</t>
+          <t>0,89; 4,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,87; 4,05</t>
+          <t>0,87; 4,11</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,36; 5,19</t>
+          <t>1,36; 5,16</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,36; 3,73</t>
+          <t>1,35; 3,65</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,88; 7,32</t>
+          <t>3,94; 7,46</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,43; 5,4</t>
+          <t>2,4; 5,39</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,92; 6,06</t>
+          <t>1,91; 5,72</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,88; 8,87</t>
+          <t>3,8; 8,73</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,76; 15,86</t>
+          <t>8,75; 15,95</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,9</t>
+          <t>0,0; 1,96</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,26; 2,48</t>
+          <t>0,24; 2,44</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,1; 10,59</t>
+          <t>4,78; 10,34</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,16</t>
+          <t>1,04; 3,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,24; 4,7</t>
+          <t>2,32; 4,84</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,53; 11,75</t>
+          <t>7,56; 12,08</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,38; 8,01</t>
+          <t>1,7; 8,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,58</t>
+          <t>0,0; 3,73</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,22; 7,36</t>
+          <t>2,14; 7,36</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,97</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,58</t>
+          <t>0,4; 3,55</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,04; 7,43</t>
+          <t>2,34; 7,38</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,86; 3,94</t>
+          <t>0,86; 4,07</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,84</t>
+          <t>0,46; 2,61</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,49; 6,21</t>
+          <t>2,34; 6,02</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,18; 7,04</t>
+          <t>2,23; 7,08</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3,09; 8,71</t>
+          <t>2,94; 8,8</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,22; 7,5</t>
+          <t>2,22; 7,22</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,74; 4,47</t>
+          <t>0,75; 4,4</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,13</t>
+          <t>0,36; 3,34</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,33; 3,01</t>
+          <t>0,32; 2,98</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,01; 4,95</t>
+          <t>1,85; 4,96</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,09; 5,36</t>
+          <t>2,09; 5,6</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,44; 4,2</t>
+          <t>1,46; 4,25</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,45; 7,31</t>
+          <t>3,43; 7,42</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,08; 9,0</t>
+          <t>5,02; 8,95</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9,99; 15,21</t>
+          <t>9,89; 14,96</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,37; 6,92</t>
+          <t>3,51; 7,21</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,21; 8,15</t>
+          <t>4,37; 8,27</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,31; 10,59</t>
+          <t>6,41; 10,65</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,8; 6,39</t>
+          <t>3,81; 6,45</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,09; 7,94</t>
+          <t>5,24; 8,1</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>8,62; 11,99</t>
+          <t>8,73; 12,18</t>
         </is>
       </c>
     </row>
@@ -1448,37 +1448,37 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,18; 6,53</t>
+          <t>3,19; 6,69</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,63; 2,18</t>
+          <t>0,62; 2,17</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8,55; 12,78</t>
+          <t>8,37; 12,9</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,58; 4,11</t>
+          <t>1,6; 4,08</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,4; 1,87</t>
+          <t>0,47; 2,15</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,24; 14,97</t>
+          <t>10,1; 14,82</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,64; 4,73</t>
+          <t>2,72; 4,66</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>9,9; 12,93</t>
+          <t>9,98; 13,19</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3,05; 4,34</t>
+          <t>2,95; 4,37</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,51; 4,95</t>
+          <t>3,49; 4,91</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6,58; 8,27</t>
+          <t>6,58; 8,41</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,64; 2,64</t>
+          <t>1,65; 2,66</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,83; 2,94</t>
+          <t>1,8; 2,88</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,23; 6,89</t>
+          <t>5,39; 7,04</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,45; 3,28</t>
+          <t>2,43; 3,26</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2,83; 3,67</t>
+          <t>2,86; 3,7</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6,1; 7,35</t>
+          <t>6,1; 7,32</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1654,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que desayuna, al menos, alimentos como huevos, queso, jamón</t>
+          <t>Población que desayuna, al menos, alimentos como huevos, queso, jamón (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>951; 9407</t>
+          <t>945; 9721</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1785; 11358</t>
+          <t>1906; 11508</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5196; 19073</t>
+          <t>5098; 17949</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 4947</t>
+          <t>0; 4980</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1125; 10297</t>
+          <t>1133; 10958</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1760; 10623</t>
+          <t>1809; 11042</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1886; 10605</t>
+          <t>1895; 10596</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4407; 18473</t>
+          <t>4249; 18036</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>8962; 23976</t>
+          <t>9291; 24689</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3163; 18116</t>
+          <t>3736; 18004</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8367; 23431</t>
+          <t>8769; 23946</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 5043</t>
+          <t>0; 5090</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>929; 8641</t>
+          <t>924; 8878</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4870; 21301</t>
+          <t>4831; 20887</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 2071</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5987; 22859</t>
+          <t>5797; 21668</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>16596; 38728</t>
+          <t>17074; 37413</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 4669</t>
+          <t>0; 5544</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4007; 15190</t>
+          <t>4022; 16274</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>20208; 39796</t>
+          <t>20056; 40895</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8766; 23911</t>
+          <t>9312; 23998</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2966; 13534</t>
+          <t>2998; 14223</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2957; 13828</t>
+          <t>2954; 14030</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4579; 17466</t>
+          <t>4577; 17359</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8902; 24430</t>
+          <t>8802; 23905</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>25800; 48604</t>
+          <t>26180; 49558</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>15905; 35367</t>
+          <t>15685; 35296</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6872; 21671</t>
+          <t>6846; 20469</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14457; 33094</t>
+          <t>14175; 32561</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>32422; 58683</t>
+          <t>32381; 59006</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 7065</t>
+          <t>0; 7274</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1018; 9648</t>
+          <t>925; 9486</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19743; 41022</t>
+          <t>18526; 40056</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8668; 23069</t>
+          <t>7553; 21876</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>17065; 35819</t>
+          <t>17693; 36903</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>56998; 88985</t>
+          <t>57238; 91509</t>
         </is>
       </c>
     </row>
@@ -2513,47 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2802; 16215</t>
+          <t>3445; 16500</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 7610</t>
+          <t>0; 7921</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4680; 15541</t>
+          <t>4521; 15537</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 2003</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>870; 7865</t>
+          <t>879; 7794</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4464; 16240</t>
+          <t>5112; 16123</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3503; 16134</t>
+          <t>3499; 16651</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1896; 12285</t>
+          <t>1972; 11279</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>10695; 26675</t>
+          <t>10062; 25873</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>5895; 19061</t>
+          <t>6040; 19182</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>8479; 23853</t>
+          <t>8044; 24116</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5852; 19732</t>
+          <t>5835; 18993</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2055; 12444</t>
+          <t>2073; 12225</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>991; 8741</t>
+          <t>991; 9319</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>905; 8189</t>
+          <t>873; 8090</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11020; 27184</t>
+          <t>10152; 27241</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>11583; 29637</t>
+          <t>11570; 30986</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>7716; 22490</t>
+          <t>7818; 22751</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>21167; 44799</t>
+          <t>21036; 45473</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>33651; 59657</t>
+          <t>33278; 59319</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>65395; 99600</t>
+          <t>64786; 97985</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>21441; 44018</t>
+          <t>22314; 45846</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>29224; 56543</t>
+          <t>30348; 57395</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>43520; 72981</t>
+          <t>44148; 73415</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>47427; 79870</t>
+          <t>47636; 80621</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>69004; 107686</t>
+          <t>71033; 109943</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>115801; 161194</t>
+          <t>117336; 163764</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>23647; 48571</t>
+          <t>23738; 49797</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>4911; 16917</t>
+          <t>4812; 16853</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>66570; 99478</t>
+          <t>65202; 100408</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>12401; 32194</t>
+          <t>12532; 31964</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>3250; 15342</t>
+          <t>3850; 17694</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>84599; 123689</t>
+          <t>83450; 122413</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>40249; 72295</t>
+          <t>41594; 71119</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>10061; 26382</t>
+          <t>10113; 26397</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>158840; 207500</t>
+          <t>160138; 211651</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>99597; 142048</t>
+          <t>96616; 143034</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>119929; 169409</t>
+          <t>119496; 167878</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>223198; 280357</t>
+          <t>223018; 285211</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>55194; 89177</t>
+          <t>55733; 89664</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>65029; 104497</t>
+          <t>64011; 102198</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>185120; 243954</t>
+          <t>190784; 249273</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>162591; 218052</t>
+          <t>161452; 216795</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>197467; 256117</t>
+          <t>199328; 258091</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>422647; 509481</t>
+          <t>422754; 507743</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P36$huevo-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P36$huevo-Provincia-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,58</t>
+          <t>0,35; 3,23</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,65; 3,9</t>
+          <t>0,63; 3,94</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,74; 6,11</t>
+          <t>1,86; 6,48</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,92</t>
+          <t>0,0; 1,94</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,83</t>
+          <t>0,39; 3,6</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,63; 3,82</t>
+          <t>0,66; 4,13</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,0</t>
+          <t>0,35; 2,01</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,73; 3,1</t>
+          <t>0,77; 3,09</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,6; 4,24</t>
+          <t>1,48; 4,15</t>
         </is>
       </c>
     </row>
@@ -788,27 +788,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,76; 3,66</t>
+          <t>0,62; 3,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,74; 4,75</t>
+          <t>1,73; 4,71</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,02</t>
+          <t>0,0; 1,09</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,76</t>
+          <t>0,19; 1,79</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,93; 4,0</t>
+          <t>0,96; 4,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -818,17 +818,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,18</t>
+          <t>0,59; 2,28</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,66; 3,65</t>
+          <t>1,62; 3,81</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,54</t>
+          <t>0,0; 0,47</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,26; 5,1</t>
+          <t>1,25; 4,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,21; 12,66</t>
+          <t>6,21; 12,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,92; 7,53</t>
+          <t>2,75; 7,21</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,89; 4,24</t>
+          <t>0,89; 4,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,87; 4,11</t>
+          <t>0,89; 4,16</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,36; 5,16</t>
+          <t>1,33; 5,13</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,35; 3,65</t>
+          <t>1,38; 3,71</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,94; 7,46</t>
+          <t>3,9; 7,28</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,4; 5,39</t>
+          <t>2,61; 5,47</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,91; 5,72</t>
+          <t>1,89; 5,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,8; 8,73</t>
+          <t>3,96; 8,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,75; 15,95</t>
+          <t>8,88; 15,81</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,96</t>
+          <t>0,0; 1,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,44</t>
+          <t>0,24; 2,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,78; 10,34</t>
+          <t>4,84; 10,49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,04; 3,0</t>
+          <t>1,15; 3,06</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,32; 4,84</t>
+          <t>2,28; 4,93</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7,56; 12,08</t>
+          <t>7,72; 11,84</t>
         </is>
       </c>
     </row>
@@ -1118,17 +1118,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,7; 8,15</t>
+          <t>1,78; 8,08</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,73</t>
+          <t>0,0; 4,14</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,14; 7,36</t>
+          <t>2,18; 7,73</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1138,27 +1138,27 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,55</t>
+          <t>0,4; 3,6</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,34; 7,38</t>
+          <t>2,04; 7,43</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,86; 4,07</t>
+          <t>0,85; 4,21</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,46; 2,61</t>
+          <t>0,45; 2,69</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,34; 6,02</t>
+          <t>2,54; 6,08</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,23; 7,08</t>
+          <t>2,16; 7,33</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,94; 8,8</t>
+          <t>3,12; 8,95</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2,22; 7,22</t>
+          <t>2,42; 7,41</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,75; 4,4</t>
+          <t>0,91; 4,41</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,34</t>
+          <t>0,35; 3,47</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,98</t>
+          <t>0,32; 2,73</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,85; 4,96</t>
+          <t>1,84; 4,73</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,09; 5,6</t>
+          <t>2,11; 5,25</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,46; 4,25</t>
+          <t>1,45; 4,11</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,43; 7,42</t>
+          <t>3,48; 7,2</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,02; 8,95</t>
+          <t>5,03; 9,31</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9,89; 14,96</t>
+          <t>9,89; 15,2</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,51; 7,21</t>
+          <t>3,42; 6,99</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,37; 8,27</t>
+          <t>4,31; 8,35</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,41; 10,65</t>
+          <t>6,43; 10,65</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,81; 6,45</t>
+          <t>3,88; 6,48</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,24; 8,1</t>
+          <t>5,25; 8,22</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>8,73; 12,18</t>
+          <t>8,81; 12,16</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>3,19; 6,69</t>
+          <t>3,26; 6,58</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,62; 2,17</t>
+          <t>0,56; 2,2</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8,37; 12,9</t>
+          <t>8,46; 12,88</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,6; 4,08</t>
+          <t>1,56; 3,95</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,47; 2,15</t>
+          <t>0,43; 2,0</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,1; 14,82</t>
+          <t>10,19; 15,05</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,72; 4,66</t>
+          <t>2,74; 4,72</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,63; 1,65</t>
+          <t>0,62; 1,71</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>9,98; 13,19</t>
+          <t>10,01; 13,16</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,95; 4,37</t>
+          <t>2,94; 4,31</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,49; 4,91</t>
+          <t>3,56; 4,91</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6,58; 8,41</t>
+          <t>6,61; 8,37</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,65; 2,66</t>
+          <t>1,64; 2,63</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,8; 2,88</t>
+          <t>1,85; 2,93</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,39; 7,04</t>
+          <t>5,21; 6,89</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,43; 3,26</t>
+          <t>2,44; 3,25</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2,86; 3,7</t>
+          <t>2,83; 3,73</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6,1; 7,32</t>
+          <t>6,16; 7,39</t>
         </is>
       </c>
     </row>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>945; 9721</t>
+          <t>956; 8753</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1906; 11508</t>
+          <t>1854; 11609</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5098; 17949</t>
+          <t>5474; 19047</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 4980</t>
+          <t>0; 5045</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1133; 10958</t>
+          <t>1113; 10299</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1809; 11042</t>
+          <t>1920; 11928</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1895; 10596</t>
+          <t>1876; 10648</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4249; 18036</t>
+          <t>4450; 17963</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>9291; 24689</t>
+          <t>8642; 24179</t>
         </is>
       </c>
     </row>
@@ -2024,27 +2024,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3736; 18004</t>
+          <t>3073; 17411</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8769; 23946</t>
+          <t>8709; 23751</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 5090</t>
+          <t>0; 5452</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>924; 8878</t>
+          <t>937; 9003</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4831; 20887</t>
+          <t>4998; 20893</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -2054,17 +2054,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5797; 21668</t>
+          <t>5857; 22680</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>17074; 37413</t>
+          <t>16580; 39068</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 5544</t>
+          <t>0; 4847</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4022; 16274</t>
+          <t>3976; 15010</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>20056; 40895</t>
+          <t>20050; 40262</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9312; 23998</t>
+          <t>8776; 22978</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2998; 14223</t>
+          <t>2996; 14449</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>2954; 14030</t>
+          <t>3050; 14171</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4577; 17359</t>
+          <t>4459; 17251</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8802; 23905</t>
+          <t>9027; 24301</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>26180; 49558</t>
+          <t>25875; 48339</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>15685; 35296</t>
+          <t>17067; 35806</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6846; 20469</t>
+          <t>6749; 20811</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14175; 32561</t>
+          <t>14762; 32840</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>32381; 59006</t>
+          <t>32840; 58491</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 7274</t>
+          <t>0; 5583</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>925; 9486</t>
+          <t>918; 8745</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18526; 40056</t>
+          <t>18732; 40629</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7553; 21876</t>
+          <t>8363; 22290</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>17693; 36903</t>
+          <t>17352; 37563</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>57238; 91509</t>
+          <t>58482; 89656</t>
         </is>
       </c>
     </row>
@@ -2513,17 +2513,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3445; 16500</t>
+          <t>3596; 16355</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 7921</t>
+          <t>0; 8801</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4521; 15537</t>
+          <t>4605; 16323</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -2533,27 +2533,27 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>879; 7794</t>
+          <t>885; 7910</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5112; 16123</t>
+          <t>4451; 16241</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3499; 16651</t>
+          <t>3487; 17219</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1972; 11279</t>
+          <t>1940; 11623</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>10062; 25873</t>
+          <t>10937; 26141</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6040; 19182</t>
+          <t>5840; 19846</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>8044; 24116</t>
+          <t>8557; 24513</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5835; 18993</t>
+          <t>6371; 19500</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2073; 12225</t>
+          <t>2527; 12261</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>991; 9319</t>
+          <t>988; 9677</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>873; 8090</t>
+          <t>869; 7419</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>10152; 27241</t>
+          <t>10123; 25971</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>11570; 30986</t>
+          <t>11692; 29045</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>7818; 22751</t>
+          <t>7740; 22010</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>21036; 45473</t>
+          <t>21306; 44154</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>33278; 59319</t>
+          <t>33309; 61738</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>64786; 97985</t>
+          <t>64732; 99527</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>22314; 45846</t>
+          <t>21791; 44484</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>30348; 57395</t>
+          <t>29885; 57955</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>44148; 73415</t>
+          <t>44321; 73380</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>47636; 80621</t>
+          <t>48499; 80914</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>71033; 109943</t>
+          <t>71217; 111577</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>117336; 163764</t>
+          <t>118365; 163483</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>23738; 49797</t>
+          <t>24260; 48966</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>4812; 16853</t>
+          <t>4360; 17114</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>65202; 100408</t>
+          <t>65839; 100257</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>12532; 31964</t>
+          <t>12255; 30974</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>3850; 17694</t>
+          <t>3564; 16419</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>83450; 122413</t>
+          <t>84170; 124302</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>41594; 71119</t>
+          <t>41891; 72029</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>10113; 26397</t>
+          <t>9923; 27346</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>160138; 211651</t>
+          <t>160713; 211106</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>96616; 143034</t>
+          <t>96059; 140992</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>119496; 167878</t>
+          <t>121903; 167997</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>223018; 285211</t>
+          <t>224167; 283870</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>55733; 89664</t>
+          <t>55299; 88606</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>64011; 102198</t>
+          <t>65849; 104174</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>190784; 249273</t>
+          <t>184554; 243990</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>161452; 216795</t>
+          <t>162356; 215852</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>199328; 258091</t>
+          <t>197247; 260043</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>422754; 507743</t>
+          <t>427114; 512394</t>
         </is>
       </c>
     </row>
